--- a/data/trans_orig/P21D_2_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D_2_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140068</t>
+          <t>139211</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150972</t>
+          <t>150524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116391</t>
+          <t>117065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123812</t>
+          <t>123864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>259603</t>
+          <t>259354</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>273166</t>
+          <t>272686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>19731</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197146</t>
+          <t>197452</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>208235</t>
+          <t>208749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224885</t>
+          <t>225257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235149</t>
+          <t>235414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>427837</t>
+          <t>428823</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442359</t>
+          <t>442186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89070</t>
+          <t>88915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135747</t>
+          <t>136034</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143549</t>
+          <t>143449</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228316</t>
+          <t>228002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237358</t>
+          <t>237321</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -1759,97 +1759,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1242</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2054</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1242</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4816</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3982</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1242</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4523</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139323</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>241744</t>
+          <t>241556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383414</t>
+          <t>383955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,97 +2102,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69461</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70527</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17549</t>
+          <t>17565</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>114066</t>
+          <t>113757</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122386</t>
+          <t>122396</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101572</t>
+          <t>101328</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108781</t>
+          <t>108793</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>218997</t>
+          <t>218981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>230005</t>
+          <t>229805</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>306703</t>
+          <t>306591</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>294355</t>
+          <t>293345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>302588</t>
+          <t>302169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>603507</t>
+          <t>603747</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>613189</t>
+          <t>613262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29030</t>
+          <t>33364</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33143</t>
+          <t>31239</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>546951</t>
+          <t>547311</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>319919</t>
+          <t>315585</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>346166</t>
+          <t>346031</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>869721</t>
+          <t>871625</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>899940</t>
+          <t>899335</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>59403</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>44458</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>82350</t>
+          <t>84305</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1626144</t>
+          <t>1626254</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1648715</t>
+          <t>1649240</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1535192</t>
+          <t>1532753</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1566211</t>
+          <t>1565875</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3173584</t>
+          <t>3171629</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3210829</t>
+          <t>3211476</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_2_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D_2_R-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15055</t>
+          <t>23270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>24290</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>34953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>146491</t>
+          <t>140976</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139211</t>
+          <t>131017</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150524</t>
+          <t>146912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>121535</t>
+          <t>127730</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117065</t>
+          <t>118451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123864</t>
+          <t>132563</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>268026</t>
+          <t>268706</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>259354</t>
+          <t>258043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>272686</t>
+          <t>277327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19731</t>
+          <t>24417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>204433</t>
+          <t>213644</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197452</t>
+          <t>205254</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>208749</t>
+          <t>218468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>232061</t>
+          <t>246770</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>225257</t>
+          <t>239090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235414</t>
+          <t>250132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>436493</t>
+          <t>460414</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>428823</t>
+          <t>450031</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442186</t>
+          <t>466293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93219</t>
+          <t>91470</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88915</t>
+          <t>87541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>140685</t>
+          <t>141525</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136034</t>
+          <t>137080</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143449</t>
+          <t>144414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>233904</t>
+          <t>232995</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228002</t>
+          <t>227700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237321</t>
+          <t>236179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>245318</t>
+          <t>200216</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>241556</t>
+          <t>197218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>386695</t>
+          <t>374676</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383955</t>
+          <t>371121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>119292</t>
+          <t>119406</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113757</t>
+          <t>113842</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122396</t>
+          <t>122993</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>106254</t>
+          <t>108850</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101328</t>
+          <t>103618</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108793</t>
+          <t>111509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>225545</t>
+          <t>228255</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>218981</t>
+          <t>222109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>229805</t>
+          <t>233446</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>310660</t>
+          <t>351709</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>306591</t>
+          <t>346859</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>299229</t>
+          <t>347167</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>293345</t>
+          <t>341399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>302169</t>
+          <t>350928</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>609889</t>
+          <t>698876</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>603747</t>
+          <t>691771</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>613262</t>
+          <t>702774</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>305195</t>
+          <t>354505</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>305195</t>
+          <t>354505</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>305195</t>
+          <t>354505</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>616931</t>
+          <t>707312</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>616931</t>
+          <t>707312</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>616931</t>
+          <t>707312</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31239</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3239,27 +3239,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>552115</t>
+          <t>358646</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>547311</t>
+          <t>354058</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>339280</t>
+          <t>402412</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>315585</t>
+          <t>396840</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>346031</t>
+          <t>405479</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>891395</t>
+          <t>761058</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>871625</t>
+          <t>754344</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>899335</t>
+          <t>765287</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>348949</t>
+          <t>407729</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>902864</t>
+          <t>768396</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>24192</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26281</t>
+          <t>30641</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>60451</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>84305</t>
+          <t>91886</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1638291</t>
+          <t>1534733</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1626254</t>
+          <t>1520127</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1649240</t>
+          <t>1544082</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1555723</t>
+          <t>1654056</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1532753</t>
+          <t>1640459</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1565875</t>
+          <t>1663970</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3194013</t>
+          <t>3188789</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3171629</t>
+          <t>3170999</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3211476</t>
+          <t>3202434</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1592156</t>
+          <t>1694611</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3255934</t>
+          <t>3262885</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
